--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11090.8</v>
+        <v>11033.82</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2065.02</v>
+        <v>2079.91</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10621.84</v>
+        <v>10696.81</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2109.06</v>
+        <v>2111.76</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9078.24</v>
+        <v>9127.889999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>32308.95</v>
+        <v>33288.65</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9162.68</v>
+        <v>9153.23</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7737.37</v>
+        <v>7729.39</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6747.82</v>
+        <v>6782.76</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>30837.49</v>
+        <v>30997.14</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21243.12</v>
+        <v>21356.08</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1016.48</v>
+        <v>1035.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2948-309-CM25</t>
+          <t>2945-1310-CM24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11033.82</v>
+        <v>10430.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1346281-187-CM25</t>
+          <t>3447-466-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.544.929-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2079.91</v>
+        <v>24006.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2948-351-CM25</t>
+          <t>2404-586-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10696.81</v>
+        <v>13263.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1346281-206-CM25</t>
+          <t>3447-2008-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2111.76</v>
+        <v>7903.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3170-4119-CM25</t>
+          <t>1346281-104-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9127.889999999999</v>
+        <v>1283.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>628-14-CM26</t>
+          <t>3447-4301-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>COMERCIALIZADORA DE ALIMENTOS, NUTRIENTES E INSUMO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>76.086.115-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>33288.65</v>
+        <v>7009.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3349-39-CM26</t>
+          <t>5126-108-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9153.23</v>
+        <v>2088.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3349-40-CM26</t>
+          <t>2404-1346-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7729.39</v>
+        <v>28175.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2404-203-CM26</t>
+          <t>2948-309-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6782.76</v>
+        <v>11033.82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2404-204-CM26</t>
+          <t>1346281-187-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>30997.14</v>
+        <v>2079.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3349-158-CM26</t>
+          <t>2948-351-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21356.08</v>
+        <v>10696.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1346281-88-CM26</t>
+          <t>1346281-206-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1240,7 +1240,678 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
+        <v>2111.76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3170-4119-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.941.300-8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>9127.889999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>628-14-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>VENTIA SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.798.686-4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>33288.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3349-39-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>9153.23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3349-40-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>7729.39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2404-203-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>6782.76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2404-204-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>VENTIA SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.798.686-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>30997.14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3349-158-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>21356.08</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1346281-88-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
         <v>1035.81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2404-1088-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>792.33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3349-289-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>20792.87</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2404-1110-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>9882.92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>628-14-CM26</t>
+          <t>3349-40-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>33288.65</v>
+        <v>7729.39</v>
       </c>
     </row>
     <row r="16">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3349-40-CM26</t>
+          <t>2404-203-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7729.39</v>
+        <v>6782.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2404-203-CM26</t>
+          <t>2404-204-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6782.76</v>
+        <v>30997.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2404-204-CM26</t>
+          <t>3349-158-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>30997.14</v>
+        <v>21356.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3349-158-CM26</t>
+          <t>1346281-88-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>21356.08</v>
+        <v>1035.81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1346281-88-CM26</t>
+          <t>2404-1088-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1035.81</v>
+        <v>792.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2404-1088-CM26</t>
+          <t>3349-289-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>792.33</v>
+        <v>20792.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3349-289-CM26</t>
+          <t>2404-1110-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>20792.87</v>
+        <v>9882.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2404-1110-CM26</t>
+          <t>935934-207-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,7 +1911,68 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9882.92</v>
+        <v>382.46</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1346281-139-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1460.91</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
@@ -623,7 +623,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1493,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1558,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1745,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1871,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/tarapaca.xlsx
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
